--- a/개발문서/결재목록.xlsx
+++ b/개발문서/결재목록.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\네이버자동주문\개발문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35EEE25-C040-4176-A659-151EC76B8B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582B6FA1-5096-429C-886D-AFE23F5DA941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24615" yWindow="3060" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
   <si>
     <t>수취인</t>
   </si>
@@ -67,12 +67,6 @@
     <t>M1</t>
   </si>
   <si>
-    <t>남유네 서리태환 플러스 3g x14포+마스크팩</t>
-  </si>
-  <si>
-    <t>허니스타</t>
-  </si>
-  <si>
     <t>R5CX349NTSF</t>
   </si>
   <si>
@@ -295,20 +289,23 @@
     <t>결재방식</t>
   </si>
   <si>
-    <t>포인트</t>
-  </si>
-  <si>
     <t>무통장</t>
   </si>
   <si>
     <t>로그인아이디</t>
+  </si>
+  <si>
+    <t>huangmeiling0209</t>
+  </si>
+  <si>
+    <t>huangmeiling1990</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,12 +319,6 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Courier New"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -350,7 +341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -360,7 +351,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -703,10 +693,10 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
+        <v>87</v>
+      </c>
+      <c r="K1" t="s">
         <v>89</v>
-      </c>
-      <c r="K1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -726,18 +716,21 @@
         <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
       </c>
       <c r="I2">
         <v>271312</v>
       </c>
       <c r="J2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K2" t="s">
         <v>90</v>
       </c>
     </row>
@@ -752,263 +745,266 @@
         <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
       </c>
       <c r="I3">
         <v>271312</v>
       </c>
       <c r="J3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="E4" t="s">
         <v>22</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="E5" t="s">
         <v>26</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
+      <c r="E6" t="s">
         <v>30</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
+      <c r="E7" t="s">
         <v>34</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" t="s">
+      <c r="E8" t="s">
         <v>38</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B9" t="s">
+      <c r="E9" t="s">
         <v>42</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B10" t="s">
+      <c r="E10" t="s">
         <v>46</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B11" t="s">
+      <c r="E11" t="s">
         <v>50</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B12" t="s">
+      <c r="E12" t="s">
         <v>54</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B13" t="s">
+      <c r="E13" t="s">
         <v>58</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B14" t="s">
+      <c r="E14" t="s">
         <v>62</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B15" t="s">
+      <c r="E15" t="s">
         <v>66</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B16" t="s">
+      <c r="E16" t="s">
         <v>70</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B17" t="s">
+      <c r="E17" t="s">
         <v>74</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B18" t="s">
+      <c r="E18" t="s">
         <v>78</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E18" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B19" t="s">
+      <c r="E19" t="s">
         <v>82</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E19" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B20" t="s">
+      <c r="E20" t="s">
         <v>86</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E20" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:5">

--- a/개발문서/결재목록.xlsx
+++ b/개발문서/결재목록.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\네이버자동주문\개발문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582B6FA1-5096-429C-886D-AFE23F5DA941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053CCEDC-2C29-44C9-BD2F-066E383484F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24615" yWindow="3060" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3180" yWindow="4740" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="93">
   <si>
     <t>수취인</t>
   </si>
@@ -52,34 +52,46 @@
     <t>비밀번호</t>
   </si>
   <si>
+    <t>결재방식</t>
+  </si>
+  <si>
+    <t>로그인아이디</t>
+  </si>
+  <si>
     <t>우진국</t>
   </si>
   <si>
     <t>010-2505-9842</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>R3CR60FENNH</t>
   </si>
   <si>
     <t>M1</t>
   </si>
   <si>
+    <t>와이유 8합사 낚시줄</t>
+  </si>
+  <si>
+    <t>와이유 구매대행</t>
+  </si>
+  <si>
+    <t>와이유 8합사 낚시줄 100m pe</t>
+  </si>
+  <si>
+    <t>무통장</t>
+  </si>
+  <si>
+    <t>huangmeiling0209</t>
+  </si>
+  <si>
     <t>R5CX349NTSF</t>
   </si>
   <si>
     <t>M2</t>
   </si>
   <si>
-    <t>와이유 8합사 낚시줄</t>
-  </si>
-  <si>
-    <t>와이유 구매대행</t>
-  </si>
-  <si>
-    <t>와이유 8합사 낚시줄 100m pe</t>
+    <t>huangmeiling1990</t>
   </si>
   <si>
     <t>박선희</t>
@@ -286,19 +298,10 @@
     <t>M20</t>
   </si>
   <si>
-    <t>결재방식</t>
-  </si>
-  <si>
-    <t>무통장</t>
-  </si>
-  <si>
-    <t>로그인아이디</t>
-  </si>
-  <si>
-    <t>huangmeiling0209</t>
-  </si>
-  <si>
-    <t>huangmeiling1990</t>
+    <t>김일</t>
+  </si>
+  <si>
+    <t>010-0000-8888</t>
   </si>
 </sst>
 </file>
@@ -693,318 +696,312 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
       </c>
       <c r="I2">
         <v>271312</v>
       </c>
       <c r="J2" t="s">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>90</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
       </c>
       <c r="I3">
         <v>271312</v>
       </c>
       <c r="J3" t="s">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K3" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:5">

--- a/개발문서/결재목록.xlsx
+++ b/개발문서/결재목록.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/개발문서/결재목록.xlsx
+++ b/개발문서/결재목록.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3180" yWindow="4740" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -562,11 +562,6 @@
       <c r="B3" s="1" t="inlineStr">
         <is>
           <t>010-0000-8888</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">

--- a/개발문서/결재목록.xlsx
+++ b/개발문서/결재목록.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">

--- a/개발문서/결재목록.xlsx
+++ b/개발문서/결재목록.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\네이버자동주문\개발문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D85F695-1A13-412B-BECB-59D57FC1DEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55BE985-4269-49F3-8A82-6D98A7FE209D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/개발문서/결재목록.xlsx
+++ b/개발문서/결재목록.xlsx
@@ -1,12 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="18240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결재방식" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$D$1:$D$20</definedName>
@@ -18,20 +19,33 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri Light"/>
+      <name val="맑은 고딕"/>
       <charset val="129"/>
       <family val="3"/>
       <sz val="11"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <color rgb="FFCE9178"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -54,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -64,9 +78,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -430,14 +447,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="16.42578125" customWidth="1" min="2" max="2"/>
-    <col width="15.42578125" customWidth="1" min="3" max="3"/>
+    <col width="16.375" customWidth="1" min="2" max="2"/>
+    <col width="15.375" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" style="4" min="4" max="4"/>
-    <col width="41.85546875" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="17.5703125" customWidth="1" min="7" max="7"/>
-    <col width="41.7109375" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="41.875" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="17.625" customWidth="1" min="7" max="7"/>
+    <col width="41.75" bestFit="1" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -511,7 +528,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -544,7 +561,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>무통장</t>
+          <t>머니</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -566,7 +583,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -599,7 +616,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>무통장</t>
+          <t>머니</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1003,4 +1020,33 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>무통장</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>머니</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
 </file>
--- a/개발문서/결재목록.xlsx
+++ b/개발문서/결재목록.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOURCE\WOO\COUPANG\네이버자동주문\개발문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BEB98F-2038-4ECC-AEEC-C3A6A06882D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6362208F-6D92-4868-A043-EEBF7101F300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28185" yWindow="4545" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="96">
   <si>
     <t>수취인</t>
   </si>
@@ -59,16 +59,16 @@
     <t>로그인아이디</t>
   </si>
   <si>
-    <t>우진국</t>
-  </si>
-  <si>
-    <t>010-2505-9842</t>
+    <t>황미여</t>
+  </si>
+  <si>
+    <t>010-3655-8742</t>
   </si>
   <si>
     <t>F</t>
   </si>
   <si>
-    <t>R3CR60FENNH</t>
+    <t>R3CR302DWEH</t>
   </si>
   <si>
     <t>M1</t>
@@ -104,12 +104,15 @@
     <t>huangmeiling1990</t>
   </si>
   <si>
-    <t>R3CW50A6R5K</t>
-  </si>
-  <si>
     <t>M3</t>
   </si>
   <si>
+    <t>포인트</t>
+  </si>
+  <si>
+    <t>bangbs0814</t>
+  </si>
+  <si>
     <t>고광석</t>
   </si>
   <si>
@@ -305,23 +308,11 @@
     <t>무통장</t>
   </si>
   <si>
-    <t>포인트</t>
+    <t>김종국</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>bangbs0814</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김오늠</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>010-16542987</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>포인트</t>
+    <t>010-1654-2987</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -811,16 +802,16 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
         <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -835,234 +826,234 @@
         <v>271312</v>
       </c>
       <c r="J4" t="s">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="K4" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1096,7 +1087,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
@@ -1106,7 +1097,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/개발문서/결재목록.xlsx
+++ b/개발문서/결재목록.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28185" yWindow="4545" windowWidth="21600" windowHeight="12645" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="18240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>

--- a/개발문서/결재목록.xlsx
+++ b/개발문서/결재목록.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOURCE\WOO\COUPANG\네이버자동주문\개발문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBB1140-8CBE-4669-B446-D1C43EE61F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16B2A3D-D031-44CA-8E0F-297974A884C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="147">
   <si>
     <t>수취인</t>
   </si>
@@ -463,7 +463,8 @@
     <t>배소현</t>
   </si>
   <si>
-    <t>사</t>
+    <t>2차비밀번호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1080,19 +1081,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M178"/>
+  <dimension ref="A1:L178"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="19.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.375" customWidth="1"/>
     <col min="3" max="3" width="15.375" customWidth="1"/>
     <col min="4" max="4" width="23" style="2" customWidth="1"/>
     <col min="6" max="6" width="41.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="78.375" customWidth="1"/>
+    <col min="10" max="10" width="12.625" customWidth="1"/>
     <col min="11" max="11" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1126,8 +1130,11 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>11</v>
       </c>
@@ -1149,17 +1156,17 @@
       <c r="H2" t="s">
         <v>17</v>
       </c>
+      <c r="I2">
+        <v>115080</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
       <c r="K2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="L2">
-        <v>115080</v>
-      </c>
-      <c r="M2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>20</v>
       </c>
@@ -1181,17 +1188,17 @@
       <c r="H3" t="s">
         <v>17</v>
       </c>
+      <c r="I3">
+        <v>115080</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
       <c r="K3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L3">
-        <v>115080</v>
-      </c>
-      <c r="M3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>22</v>
       </c>
@@ -1213,17 +1220,17 @@
       <c r="H4" t="s">
         <v>17</v>
       </c>
+      <c r="I4">
+        <v>115080</v>
+      </c>
+      <c r="J4" t="s">
+        <v>19</v>
+      </c>
       <c r="K4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="L4">
-        <v>115080</v>
-      </c>
-      <c r="M4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>27</v>
       </c>
@@ -1245,17 +1252,17 @@
       <c r="H5" t="s">
         <v>17</v>
       </c>
+      <c r="I5">
+        <v>115080</v>
+      </c>
+      <c r="J5" t="s">
+        <v>19</v>
+      </c>
       <c r="K5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="L5">
-        <v>115080</v>
-      </c>
-      <c r="M5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>29</v>
       </c>
@@ -1277,17 +1284,17 @@
       <c r="H6" t="s">
         <v>17</v>
       </c>
+      <c r="I6">
+        <v>115080</v>
+      </c>
+      <c r="J6" t="s">
+        <v>19</v>
+      </c>
       <c r="K6" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="L6">
-        <v>115080</v>
-      </c>
-      <c r="M6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>31</v>
       </c>
@@ -1310,17 +1317,17 @@
       <c r="H7" t="s">
         <v>17</v>
       </c>
+      <c r="I7">
+        <v>115080</v>
+      </c>
+      <c r="J7" t="s">
+        <v>19</v>
+      </c>
       <c r="K7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="L7">
-        <v>115080</v>
-      </c>
-      <c r="M7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>36</v>
       </c>
@@ -1342,17 +1349,17 @@
       <c r="H8" t="s">
         <v>17</v>
       </c>
+      <c r="I8">
+        <v>115080</v>
+      </c>
+      <c r="J8" t="s">
+        <v>19</v>
+      </c>
       <c r="K8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="L8">
-        <v>115080</v>
-      </c>
-      <c r="M8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>38</v>
       </c>
@@ -1374,17 +1381,17 @@
       <c r="H9" t="s">
         <v>17</v>
       </c>
+      <c r="I9">
+        <v>115080</v>
+      </c>
+      <c r="J9" t="s">
+        <v>19</v>
+      </c>
       <c r="K9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="L9">
-        <v>115080</v>
-      </c>
-      <c r="M9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>40</v>
       </c>
@@ -1406,17 +1413,17 @@
       <c r="H10" t="s">
         <v>17</v>
       </c>
+      <c r="I10">
+        <v>115080</v>
+      </c>
+      <c r="J10" t="s">
+        <v>19</v>
+      </c>
       <c r="K10" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="L10">
-        <v>115080</v>
-      </c>
-      <c r="M10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>45</v>
       </c>
@@ -1438,17 +1445,17 @@
       <c r="H11" t="s">
         <v>17</v>
       </c>
+      <c r="I11">
+        <v>115080</v>
+      </c>
+      <c r="J11" t="s">
+        <v>19</v>
+      </c>
       <c r="K11" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="L11">
-        <v>115080</v>
-      </c>
-      <c r="M11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>47</v>
       </c>
@@ -1470,17 +1477,17 @@
       <c r="H12" t="s">
         <v>17</v>
       </c>
+      <c r="I12">
+        <v>115080</v>
+      </c>
+      <c r="J12" t="s">
+        <v>19</v>
+      </c>
       <c r="K12" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="L12">
-        <v>115080</v>
-      </c>
-      <c r="M12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>49</v>
       </c>
@@ -1502,17 +1509,17 @@
       <c r="H13" t="s">
         <v>17</v>
       </c>
+      <c r="I13">
+        <v>115080</v>
+      </c>
+      <c r="J13" t="s">
+        <v>19</v>
+      </c>
       <c r="K13" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="L13">
-        <v>115080</v>
-      </c>
-      <c r="M13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>54</v>
       </c>
@@ -1534,17 +1541,17 @@
       <c r="H14" t="s">
         <v>17</v>
       </c>
+      <c r="I14">
+        <v>115080</v>
+      </c>
+      <c r="J14" t="s">
+        <v>19</v>
+      </c>
       <c r="K14" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="L14">
-        <v>115080</v>
-      </c>
-      <c r="M14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>56</v>
       </c>
@@ -1566,17 +1573,17 @@
       <c r="H15" t="s">
         <v>17</v>
       </c>
+      <c r="I15">
+        <v>115080</v>
+      </c>
+      <c r="J15" t="s">
+        <v>19</v>
+      </c>
       <c r="K15" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="L15">
-        <v>115080</v>
-      </c>
-      <c r="M15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>58</v>
       </c>
@@ -1598,17 +1605,17 @@
       <c r="H16" t="s">
         <v>17</v>
       </c>
+      <c r="I16">
+        <v>115080</v>
+      </c>
+      <c r="J16" t="s">
+        <v>19</v>
+      </c>
       <c r="K16" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="L16">
-        <v>115080</v>
-      </c>
-      <c r="M16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>63</v>
       </c>
@@ -1630,17 +1637,17 @@
       <c r="H17" t="s">
         <v>17</v>
       </c>
+      <c r="I17">
+        <v>115080</v>
+      </c>
+      <c r="J17" t="s">
+        <v>19</v>
+      </c>
       <c r="K17" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="L17">
-        <v>115080</v>
-      </c>
-      <c r="M17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
         <v>65</v>
       </c>
@@ -1662,17 +1669,17 @@
       <c r="H18" t="s">
         <v>17</v>
       </c>
+      <c r="I18">
+        <v>115080</v>
+      </c>
+      <c r="J18" t="s">
+        <v>19</v>
+      </c>
       <c r="K18" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="L18">
-        <v>115080</v>
-      </c>
-      <c r="M18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>67</v>
       </c>
@@ -1694,17 +1701,17 @@
       <c r="H19" t="s">
         <v>17</v>
       </c>
+      <c r="I19">
+        <v>115080</v>
+      </c>
+      <c r="J19" t="s">
+        <v>19</v>
+      </c>
       <c r="K19" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="L19">
-        <v>115080</v>
-      </c>
-      <c r="M19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>72</v>
       </c>
@@ -1726,17 +1733,17 @@
       <c r="H20" t="s">
         <v>17</v>
       </c>
+      <c r="I20">
+        <v>115080</v>
+      </c>
+      <c r="J20" t="s">
+        <v>19</v>
+      </c>
       <c r="K20" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="L20">
-        <v>115080</v>
-      </c>
-      <c r="M20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>74</v>
       </c>
@@ -1758,17 +1765,17 @@
       <c r="H21" t="s">
         <v>17</v>
       </c>
+      <c r="I21">
+        <v>115080</v>
+      </c>
+      <c r="J21" t="s">
+        <v>19</v>
+      </c>
       <c r="K21" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="L21">
-        <v>115080</v>
-      </c>
-      <c r="M21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
         <v>76</v>
       </c>
@@ -1790,17 +1797,17 @@
       <c r="H22" t="s">
         <v>17</v>
       </c>
+      <c r="I22">
+        <v>115080</v>
+      </c>
+      <c r="J22" t="s">
+        <v>19</v>
+      </c>
       <c r="K22" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="L22">
-        <v>115080</v>
-      </c>
-      <c r="M22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>81</v>
       </c>
@@ -1822,17 +1829,17 @@
       <c r="H23" t="s">
         <v>17</v>
       </c>
+      <c r="I23">
+        <v>115080</v>
+      </c>
+      <c r="J23" t="s">
+        <v>19</v>
+      </c>
       <c r="K23" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="L23">
-        <v>115080</v>
-      </c>
-      <c r="M23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
         <v>83</v>
       </c>
@@ -1854,17 +1861,17 @@
       <c r="H24" t="s">
         <v>17</v>
       </c>
+      <c r="I24">
+        <v>115080</v>
+      </c>
+      <c r="J24" t="s">
+        <v>19</v>
+      </c>
       <c r="K24" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="L24">
-        <v>115080</v>
-      </c>
-      <c r="M24" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>85</v>
       </c>
@@ -1886,17 +1893,17 @@
       <c r="H25" t="s">
         <v>17</v>
       </c>
+      <c r="I25">
+        <v>115080</v>
+      </c>
+      <c r="J25" t="s">
+        <v>19</v>
+      </c>
       <c r="K25" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="L25">
-        <v>115080</v>
-      </c>
-      <c r="M25" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>90</v>
       </c>
@@ -1918,17 +1925,17 @@
       <c r="H26" t="s">
         <v>17</v>
       </c>
+      <c r="I26">
+        <v>115080</v>
+      </c>
+      <c r="J26" t="s">
+        <v>19</v>
+      </c>
       <c r="K26" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L26">
-        <v>115080</v>
-      </c>
-      <c r="M26" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>92</v>
       </c>
@@ -1950,17 +1957,17 @@
       <c r="H27" t="s">
         <v>94</v>
       </c>
+      <c r="I27">
+        <v>115080</v>
+      </c>
+      <c r="J27" t="s">
+        <v>19</v>
+      </c>
       <c r="K27" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="L27">
-        <v>115080</v>
-      </c>
-      <c r="M27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>95</v>
       </c>
@@ -1982,17 +1989,17 @@
       <c r="H28" t="s">
         <v>94</v>
       </c>
+      <c r="I28">
+        <v>115080</v>
+      </c>
+      <c r="J28" t="s">
+        <v>19</v>
+      </c>
       <c r="K28" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L28">
-        <v>115080</v>
-      </c>
-      <c r="M28" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>96</v>
       </c>
@@ -2014,17 +2021,17 @@
       <c r="H29" t="s">
         <v>94</v>
       </c>
+      <c r="I29">
+        <v>115080</v>
+      </c>
+      <c r="J29" t="s">
+        <v>19</v>
+      </c>
       <c r="K29" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="L29">
-        <v>115080</v>
-      </c>
-      <c r="M29" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>97</v>
       </c>
@@ -2046,17 +2053,17 @@
       <c r="H30" t="s">
         <v>94</v>
       </c>
+      <c r="I30">
+        <v>115080</v>
+      </c>
+      <c r="J30" t="s">
+        <v>19</v>
+      </c>
       <c r="K30" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="L30">
-        <v>115080</v>
-      </c>
-      <c r="M30" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>98</v>
       </c>
@@ -2078,17 +2085,17 @@
       <c r="H31" t="s">
         <v>94</v>
       </c>
+      <c r="I31">
+        <v>115080</v>
+      </c>
+      <c r="J31" t="s">
+        <v>19</v>
+      </c>
       <c r="K31" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="L31">
-        <v>115080</v>
-      </c>
-      <c r="M31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>99</v>
       </c>
@@ -2110,17 +2117,17 @@
       <c r="H32" t="s">
         <v>94</v>
       </c>
+      <c r="I32">
+        <v>115080</v>
+      </c>
+      <c r="J32" t="s">
+        <v>19</v>
+      </c>
       <c r="K32" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="L32">
-        <v>115080</v>
-      </c>
-      <c r="M32" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>100</v>
       </c>
@@ -2142,17 +2149,17 @@
       <c r="H33" t="s">
         <v>94</v>
       </c>
+      <c r="I33">
+        <v>115080</v>
+      </c>
+      <c r="J33" t="s">
+        <v>19</v>
+      </c>
       <c r="K33" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="L33">
-        <v>115080</v>
-      </c>
-      <c r="M33" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>101</v>
       </c>
@@ -2174,17 +2181,17 @@
       <c r="H34" t="s">
         <v>94</v>
       </c>
+      <c r="I34">
+        <v>115080</v>
+      </c>
+      <c r="J34" t="s">
+        <v>19</v>
+      </c>
       <c r="K34" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="L34">
-        <v>115080</v>
-      </c>
-      <c r="M34" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>102</v>
       </c>
@@ -2206,17 +2213,17 @@
       <c r="H35" t="s">
         <v>94</v>
       </c>
+      <c r="I35">
+        <v>115080</v>
+      </c>
+      <c r="J35" t="s">
+        <v>19</v>
+      </c>
       <c r="K35" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="L35">
-        <v>115080</v>
-      </c>
-      <c r="M35" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>103</v>
       </c>
@@ -2238,17 +2245,17 @@
       <c r="H36" t="s">
         <v>94</v>
       </c>
+      <c r="I36">
+        <v>115080</v>
+      </c>
+      <c r="J36" t="s">
+        <v>19</v>
+      </c>
       <c r="K36" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="L36">
-        <v>115080</v>
-      </c>
-      <c r="M36" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>104</v>
       </c>
@@ -2270,17 +2277,17 @@
       <c r="H37" t="s">
         <v>94</v>
       </c>
+      <c r="I37">
+        <v>115080</v>
+      </c>
+      <c r="J37" t="s">
+        <v>19</v>
+      </c>
       <c r="K37" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="L37">
-        <v>115080</v>
-      </c>
-      <c r="M37" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>105</v>
       </c>
@@ -2302,17 +2309,17 @@
       <c r="H38" t="s">
         <v>94</v>
       </c>
+      <c r="I38">
+        <v>115080</v>
+      </c>
+      <c r="J38" t="s">
+        <v>19</v>
+      </c>
       <c r="K38" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="L38">
-        <v>115080</v>
-      </c>
-      <c r="M38" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>106</v>
       </c>
@@ -2334,17 +2341,17 @@
       <c r="H39" t="s">
         <v>94</v>
       </c>
+      <c r="I39">
+        <v>115080</v>
+      </c>
+      <c r="J39" t="s">
+        <v>19</v>
+      </c>
       <c r="K39" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="L39">
-        <v>115080</v>
-      </c>
-      <c r="M39" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>107</v>
       </c>
@@ -2366,17 +2373,17 @@
       <c r="H40" t="s">
         <v>94</v>
       </c>
+      <c r="I40">
+        <v>115080</v>
+      </c>
+      <c r="J40" t="s">
+        <v>19</v>
+      </c>
       <c r="K40" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="L40">
-        <v>115080</v>
-      </c>
-      <c r="M40" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>108</v>
       </c>
@@ -2398,17 +2405,17 @@
       <c r="H41" t="s">
         <v>94</v>
       </c>
+      <c r="I41">
+        <v>115080</v>
+      </c>
+      <c r="J41" t="s">
+        <v>19</v>
+      </c>
       <c r="K41" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="L41">
-        <v>115080</v>
-      </c>
-      <c r="M41" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>109</v>
       </c>
@@ -2431,17 +2438,17 @@
       <c r="H42" t="s">
         <v>94</v>
       </c>
+      <c r="I42">
+        <v>115080</v>
+      </c>
+      <c r="J42" t="s">
+        <v>19</v>
+      </c>
       <c r="K42" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="L42">
-        <v>115080</v>
-      </c>
-      <c r="M42" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>110</v>
       </c>
@@ -2463,17 +2470,17 @@
       <c r="H43" t="s">
         <v>94</v>
       </c>
+      <c r="I43">
+        <v>115080</v>
+      </c>
+      <c r="J43" t="s">
+        <v>19</v>
+      </c>
       <c r="K43" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="L43">
-        <v>115080</v>
-      </c>
-      <c r="M43" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>111</v>
       </c>
@@ -2495,17 +2502,17 @@
       <c r="H44" t="s">
         <v>94</v>
       </c>
+      <c r="I44">
+        <v>115080</v>
+      </c>
+      <c r="J44" t="s">
+        <v>19</v>
+      </c>
       <c r="K44" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="L44">
-        <v>115080</v>
-      </c>
-      <c r="M44" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>112</v>
       </c>
@@ -2527,17 +2534,17 @@
       <c r="H45" t="s">
         <v>94</v>
       </c>
+      <c r="I45">
+        <v>115080</v>
+      </c>
+      <c r="J45" t="s">
+        <v>19</v>
+      </c>
       <c r="K45" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="L45">
-        <v>115080</v>
-      </c>
-      <c r="M45" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>113</v>
       </c>
@@ -2559,17 +2566,17 @@
       <c r="H46" t="s">
         <v>94</v>
       </c>
+      <c r="I46">
+        <v>115080</v>
+      </c>
+      <c r="J46" t="s">
+        <v>19</v>
+      </c>
       <c r="K46" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="L46">
-        <v>115080</v>
-      </c>
-      <c r="M46" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>114</v>
       </c>
@@ -2591,17 +2598,17 @@
       <c r="H47" t="s">
         <v>94</v>
       </c>
+      <c r="I47">
+        <v>115080</v>
+      </c>
+      <c r="J47" t="s">
+        <v>19</v>
+      </c>
       <c r="K47" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="L47">
-        <v>115080</v>
-      </c>
-      <c r="M47" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>115</v>
       </c>
@@ -2623,17 +2630,17 @@
       <c r="H48" t="s">
         <v>94</v>
       </c>
+      <c r="I48">
+        <v>115080</v>
+      </c>
+      <c r="J48" t="s">
+        <v>19</v>
+      </c>
       <c r="K48" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="L48">
-        <v>115080</v>
-      </c>
-      <c r="M48" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>116</v>
       </c>
@@ -2655,17 +2662,17 @@
       <c r="H49" t="s">
         <v>94</v>
       </c>
+      <c r="I49">
+        <v>115080</v>
+      </c>
+      <c r="J49" t="s">
+        <v>19</v>
+      </c>
       <c r="K49" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="L49">
-        <v>115080</v>
-      </c>
-      <c r="M49" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>117</v>
       </c>
@@ -2687,17 +2694,17 @@
       <c r="H50" t="s">
         <v>94</v>
       </c>
+      <c r="I50">
+        <v>115080</v>
+      </c>
+      <c r="J50" t="s">
+        <v>19</v>
+      </c>
       <c r="K50" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="L50">
-        <v>115080</v>
-      </c>
-      <c r="M50" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>118</v>
       </c>
@@ -2719,17 +2726,17 @@
       <c r="H51" t="s">
         <v>94</v>
       </c>
+      <c r="I51">
+        <v>115080</v>
+      </c>
+      <c r="J51" t="s">
+        <v>19</v>
+      </c>
       <c r="K51" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L51">
-        <v>115080</v>
-      </c>
-      <c r="M51" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>119</v>
       </c>
@@ -2751,17 +2758,17 @@
       <c r="H52" t="s">
         <v>121</v>
       </c>
+      <c r="I52">
+        <v>115080</v>
+      </c>
+      <c r="J52" t="s">
+        <v>19</v>
+      </c>
       <c r="K52" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="L52">
-        <v>115080</v>
-      </c>
-      <c r="M52" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>122</v>
       </c>
@@ -2783,17 +2790,17 @@
       <c r="H53" t="s">
         <v>121</v>
       </c>
+      <c r="I53">
+        <v>115080</v>
+      </c>
+      <c r="J53" t="s">
+        <v>19</v>
+      </c>
       <c r="K53" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L53">
-        <v>115080</v>
-      </c>
-      <c r="M53" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>123</v>
       </c>
@@ -2815,17 +2822,17 @@
       <c r="H54" t="s">
         <v>121</v>
       </c>
+      <c r="I54">
+        <v>115080</v>
+      </c>
+      <c r="J54" t="s">
+        <v>19</v>
+      </c>
       <c r="K54" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="L54">
-        <v>115080</v>
-      </c>
-      <c r="M54" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>124</v>
       </c>
@@ -2847,17 +2854,17 @@
       <c r="H55" t="s">
         <v>121</v>
       </c>
+      <c r="I55">
+        <v>115080</v>
+      </c>
+      <c r="J55" t="s">
+        <v>19</v>
+      </c>
       <c r="K55" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="L55">
-        <v>115080</v>
-      </c>
-      <c r="M55" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>125</v>
       </c>
@@ -2879,17 +2886,17 @@
       <c r="H56" t="s">
         <v>121</v>
       </c>
+      <c r="I56">
+        <v>115080</v>
+      </c>
+      <c r="J56" t="s">
+        <v>19</v>
+      </c>
       <c r="K56" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="L56">
-        <v>115080</v>
-      </c>
-      <c r="M56" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>126</v>
       </c>
@@ -2911,17 +2918,17 @@
       <c r="H57" t="s">
         <v>121</v>
       </c>
+      <c r="I57">
+        <v>115080</v>
+      </c>
+      <c r="J57" t="s">
+        <v>19</v>
+      </c>
       <c r="K57" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="L57">
-        <v>115080</v>
-      </c>
-      <c r="M57" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>127</v>
       </c>
@@ -2943,17 +2950,17 @@
       <c r="H58" t="s">
         <v>121</v>
       </c>
+      <c r="I58">
+        <v>115080</v>
+      </c>
+      <c r="J58" t="s">
+        <v>19</v>
+      </c>
       <c r="K58" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="L58">
-        <v>115080</v>
-      </c>
-      <c r="M58" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>128</v>
       </c>
@@ -2975,17 +2982,17 @@
       <c r="H59" t="s">
         <v>121</v>
       </c>
+      <c r="I59">
+        <v>115080</v>
+      </c>
+      <c r="J59" t="s">
+        <v>19</v>
+      </c>
       <c r="K59" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="L59">
-        <v>115080</v>
-      </c>
-      <c r="M59" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>129</v>
       </c>
@@ -3007,17 +3014,17 @@
       <c r="H60" t="s">
         <v>121</v>
       </c>
+      <c r="I60">
+        <v>115080</v>
+      </c>
+      <c r="J60" t="s">
+        <v>19</v>
+      </c>
       <c r="K60" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="L60">
-        <v>115080</v>
-      </c>
-      <c r="M60" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>130</v>
       </c>
@@ -3039,17 +3046,17 @@
       <c r="H61" t="s">
         <v>121</v>
       </c>
+      <c r="I61">
+        <v>115080</v>
+      </c>
+      <c r="J61" t="s">
+        <v>19</v>
+      </c>
       <c r="K61" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="L61">
-        <v>115080</v>
-      </c>
-      <c r="M61" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>131</v>
       </c>
@@ -3071,17 +3078,17 @@
       <c r="H62" t="s">
         <v>121</v>
       </c>
+      <c r="I62">
+        <v>115080</v>
+      </c>
+      <c r="J62" t="s">
+        <v>19</v>
+      </c>
       <c r="K62" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="L62">
-        <v>115080</v>
-      </c>
-      <c r="M62" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>132</v>
       </c>
@@ -3103,17 +3110,17 @@
       <c r="H63" t="s">
         <v>121</v>
       </c>
+      <c r="I63">
+        <v>115080</v>
+      </c>
+      <c r="J63" t="s">
+        <v>19</v>
+      </c>
       <c r="K63" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="L63">
-        <v>115080</v>
-      </c>
-      <c r="M63" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>133</v>
       </c>
@@ -3135,17 +3142,17 @@
       <c r="H64" t="s">
         <v>121</v>
       </c>
+      <c r="I64">
+        <v>115080</v>
+      </c>
+      <c r="J64" t="s">
+        <v>19</v>
+      </c>
       <c r="K64" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="L64">
-        <v>115080</v>
-      </c>
-      <c r="M64" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>134</v>
       </c>
@@ -3167,17 +3174,17 @@
       <c r="H65" t="s">
         <v>121</v>
       </c>
+      <c r="I65">
+        <v>115080</v>
+      </c>
+      <c r="J65" t="s">
+        <v>19</v>
+      </c>
       <c r="K65" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="L65">
-        <v>115080</v>
-      </c>
-      <c r="M65" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>135</v>
       </c>
@@ -3199,17 +3206,17 @@
       <c r="H66" t="s">
         <v>121</v>
       </c>
+      <c r="I66">
+        <v>115080</v>
+      </c>
+      <c r="J66" t="s">
+        <v>19</v>
+      </c>
       <c r="K66" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="L66">
-        <v>115080</v>
-      </c>
-      <c r="M66" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>136</v>
       </c>
@@ -3231,17 +3238,17 @@
       <c r="H67" t="s">
         <v>121</v>
       </c>
+      <c r="I67">
+        <v>115080</v>
+      </c>
+      <c r="J67" t="s">
+        <v>19</v>
+      </c>
       <c r="K67" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="L67">
-        <v>115080</v>
-      </c>
-      <c r="M67" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>137</v>
       </c>
@@ -3263,17 +3270,17 @@
       <c r="H68" t="s">
         <v>121</v>
       </c>
+      <c r="I68">
+        <v>115080</v>
+      </c>
+      <c r="J68" t="s">
+        <v>19</v>
+      </c>
       <c r="K68" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="L68">
-        <v>115080</v>
-      </c>
-      <c r="M68" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>138</v>
       </c>
@@ -3295,17 +3302,17 @@
       <c r="H69" t="s">
         <v>121</v>
       </c>
+      <c r="I69">
+        <v>115080</v>
+      </c>
+      <c r="J69" t="s">
+        <v>19</v>
+      </c>
       <c r="K69" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="L69">
-        <v>115080</v>
-      </c>
-      <c r="M69" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>139</v>
       </c>
@@ -3327,17 +3334,17 @@
       <c r="H70" t="s">
         <v>121</v>
       </c>
+      <c r="I70">
+        <v>115080</v>
+      </c>
+      <c r="J70" t="s">
+        <v>19</v>
+      </c>
       <c r="K70" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="L70">
-        <v>115080</v>
-      </c>
-      <c r="M70" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>140</v>
       </c>
@@ -3359,17 +3366,17 @@
       <c r="H71" t="s">
         <v>121</v>
       </c>
+      <c r="I71">
+        <v>115080</v>
+      </c>
+      <c r="J71" t="s">
+        <v>19</v>
+      </c>
       <c r="K71" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="L71">
-        <v>115080</v>
-      </c>
-      <c r="M71" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>141</v>
       </c>
@@ -3391,17 +3398,17 @@
       <c r="H72" t="s">
         <v>121</v>
       </c>
+      <c r="I72">
+        <v>115080</v>
+      </c>
+      <c r="J72" t="s">
+        <v>19</v>
+      </c>
       <c r="K72" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="L72">
-        <v>115080</v>
-      </c>
-      <c r="M72" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>142</v>
       </c>
@@ -3423,17 +3430,17 @@
       <c r="H73" t="s">
         <v>121</v>
       </c>
+      <c r="I73">
+        <v>115080</v>
+      </c>
+      <c r="J73" t="s">
+        <v>19</v>
+      </c>
       <c r="K73" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="L73">
-        <v>115080</v>
-      </c>
-      <c r="M73" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>143</v>
       </c>
@@ -3455,17 +3462,17 @@
       <c r="H74" t="s">
         <v>121</v>
       </c>
+      <c r="I74">
+        <v>115080</v>
+      </c>
+      <c r="J74" t="s">
+        <v>19</v>
+      </c>
       <c r="K74" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="L74">
-        <v>115080</v>
-      </c>
-      <c r="M74" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>144</v>
       </c>
@@ -3487,17 +3494,17 @@
       <c r="H75" t="s">
         <v>121</v>
       </c>
+      <c r="I75">
+        <v>115080</v>
+      </c>
+      <c r="J75" t="s">
+        <v>19</v>
+      </c>
       <c r="K75" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="L75">
-        <v>115080</v>
-      </c>
-      <c r="M75" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>145</v>
       </c>
@@ -3511,7 +3518,7 @@
         <v>88</v>
       </c>
       <c r="F76" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="G76" t="s">
         <v>16</v>
@@ -3519,17 +3526,17 @@
       <c r="H76" t="s">
         <v>121</v>
       </c>
+      <c r="I76">
+        <v>115080</v>
+      </c>
+      <c r="J76" t="s">
+        <v>19</v>
+      </c>
       <c r="K76" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L76">
-        <v>115080</v>
-      </c>
-      <c r="M76" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="5"/>
@@ -3538,7 +3545,7 @@
       <c r="H77" s="9"/>
       <c r="K77" s="7"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B78" s="1"/>
       <c r="D78" s="5"/>
       <c r="E78" s="6"/>
@@ -3546,14 +3553,14 @@
       <c r="H78" s="9"/>
       <c r="K78" s="8"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D79" s="5"/>
       <c r="E79" s="6"/>
       <c r="F79" s="9"/>
       <c r="H79" s="9"/>
       <c r="K79" s="8"/>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D80" s="5"/>
       <c r="E80" s="6"/>
       <c r="F80" s="9"/>
@@ -4309,7 +4316,7 @@
   <conditionalFormatting sqref="A28:A178">
     <cfRule type="duplicateValues" dxfId="16" priority="102"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K1048576">
+  <conditionalFormatting sqref="K1:K1048576 L1">
     <cfRule type="duplicateValues" dxfId="15" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
